--- a/file/table/TSIG_DistanciaEstaciones.xlsx
+++ b/file/table/TSIG_DistanciaEstaciones.xlsx
@@ -1,27 +1,33 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29721"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30426"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\R.TSIG\file\table\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB610A04-324A-4070-9244-9129BFBF4E0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E80A11D8-B044-476F-B872-AF7575F180E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28898" yWindow="6562" windowWidth="28996" windowHeight="15675" xr2:uid="{19276741-97E1-4F04-AE72-7C7189CE5845}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" activeTab="1" xr2:uid="{19276741-97E1-4F04-AE72-7C7189CE5845}"/>
   </bookViews>
   <sheets>
     <sheet name="DistanciaEstaciones" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="3" r:id="rId2"/>
-    <sheet name="Sheet1" sheetId="2" r:id="rId3"/>
+    <sheet name="DistanciaMultipleEstaciones" sheetId="4" r:id="rId2"/>
+    <sheet name="Sheet2" sheetId="3" r:id="rId3"/>
+    <sheet name="Sheet1" sheetId="2" r:id="rId4"/>
   </sheets>
   <definedNames>
+    <definedName name="DeltaX" localSheetId="1">DistanciaMultipleEstaciones!#REF!</definedName>
     <definedName name="DeltaX">DistanciaEstaciones!$C$6</definedName>
+    <definedName name="DeltaY" localSheetId="1">DistanciaMultipleEstaciones!#REF!</definedName>
     <definedName name="DeltaY">DistanciaEstaciones!$D$6</definedName>
+    <definedName name="DeltaZ" localSheetId="1">DistanciaMultipleEstaciones!#REF!</definedName>
     <definedName name="DeltaZ">DistanciaEstaciones!$E$6</definedName>
+    <definedName name="Distancia2D" localSheetId="1">DistanciaMultipleEstaciones!#REF!</definedName>
     <definedName name="Distancia2D">DistanciaEstaciones!$D$12</definedName>
+    <definedName name="Distancia3D" localSheetId="1">DistanciaMultipleEstaciones!#REF!</definedName>
     <definedName name="Distancia3D">DistanciaEstaciones!$D$13</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -67,7 +73,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="84">
   <si>
     <t>Estación</t>
   </si>
@@ -274,6 +280,51 @@
   </si>
   <si>
     <t>Dirección con respecto a la horizontal de la estación más al norte.</t>
+  </si>
+  <si>
+    <t>Cálculo de distancias entre múltiples estaciones</t>
+  </si>
+  <si>
+    <t>Localización de estación o punto de referencia</t>
+  </si>
+  <si>
+    <t>Punto arbitrario</t>
+  </si>
+  <si>
+    <t>Estaciones próximas</t>
+  </si>
+  <si>
+    <t>ΔX</t>
+  </si>
+  <si>
+    <t>ΔY</t>
+  </si>
+  <si>
+    <t>ΔZ</t>
+  </si>
+  <si>
+    <t>Centroide X</t>
+  </si>
+  <si>
+    <t>Centroide Y</t>
+  </si>
+  <si>
+    <t>Centroide Z</t>
+  </si>
+  <si>
+    <t>CAMPO CAPOTE [23125040]</t>
+  </si>
+  <si>
+    <t>MELITOSA LA [23140060]</t>
+  </si>
+  <si>
+    <t>PUENTE FERROCARRIL OPÓN [23147020]</t>
+  </si>
+  <si>
+    <t>v.20260901</t>
+  </si>
+  <si>
+    <t>Promedio σ:</t>
   </si>
 </sst>
 </file>
@@ -283,7 +334,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0000"/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -306,6 +357,11 @@
     <font>
       <sz val="8"/>
       <color theme="1"/>
+      <name val="Segoe UI Light"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <name val="Segoe UI Light"/>
       <family val="2"/>
     </font>
@@ -525,7 +581,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -623,6 +679,39 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -685,6 +774,61 @@
         <a:xfrm>
           <a:off x="4432102" y="146366"/>
           <a:ext cx="1000453" cy="240423"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>398946</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>18142</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>455489</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>48359</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Graphic 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8CDCADA2-3832-458E-A6AA-D936957E7CAB}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{96DAC541-7B7A-43D3-8B79-37D633B846F1}">
+              <asvg:svgBlip xmlns:asvg="http://schemas.microsoft.com/office/drawing/2016/SVG/main" r:embed="rId2"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4186965" y="226960"/>
+          <a:ext cx="998053" cy="239034"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1227,6 +1371,523 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{88FFEC33-4080-475F-B822-E959CBA1839A}">
+  <dimension ref="A1:AF20"/>
+  <sheetFormatPr defaultColWidth="9.1328125" defaultRowHeight="16.5" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="1" width="2.6640625" style="5" customWidth="1"/>
+    <col min="2" max="2" width="37.19921875" style="4" customWidth="1"/>
+    <col min="3" max="4" width="13.19921875" style="4" customWidth="1"/>
+    <col min="5" max="5" width="7.06640625" style="4" customWidth="1"/>
+    <col min="6" max="8" width="9.46484375" style="4" customWidth="1"/>
+    <col min="9" max="12" width="10.73046875" style="4" customWidth="1"/>
+    <col min="13" max="14" width="13.265625" style="4" customWidth="1"/>
+    <col min="15" max="16384" width="9.1328125" style="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:32" x14ac:dyDescent="0.45">
+      <c r="E1" s="5" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="2" spans="1:32" x14ac:dyDescent="0.45">
+      <c r="B2" s="4" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="4" spans="1:32" x14ac:dyDescent="0.45">
+      <c r="B4" s="4" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="5" spans="1:32" x14ac:dyDescent="0.45">
+      <c r="B5" s="22" t="s">
+        <v>0</v>
+      </c>
+      <c r="C5" s="23" t="s">
+        <v>62</v>
+      </c>
+      <c r="D5" s="23" t="s">
+        <v>63</v>
+      </c>
+      <c r="E5" s="24" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="6" spans="1:32" ht="34.9" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B6" s="42" t="s">
+        <v>71</v>
+      </c>
+      <c r="C6" s="35">
+        <v>4902232</v>
+      </c>
+      <c r="D6" s="35">
+        <v>2297439</v>
+      </c>
+      <c r="E6" s="36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:32" x14ac:dyDescent="0.45">
+      <c r="B8" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="K8" s="44" t="s">
+        <v>83</v>
+      </c>
+      <c r="L8" s="4">
+        <f>AVERAGE(L10:L19)</f>
+        <v>1367991.5684213266</v>
+      </c>
+      <c r="M8" s="4">
+        <f t="shared" ref="M8:N8" si="0">AVERAGE(M10:M19)</f>
+        <v>1367991.673048208</v>
+      </c>
+      <c r="N8" s="4">
+        <f t="shared" si="0"/>
+        <v>1367991.6730482082</v>
+      </c>
+    </row>
+    <row r="9" spans="1:32" ht="49.5" x14ac:dyDescent="0.45">
+      <c r="B9" s="39" t="s">
+        <v>0</v>
+      </c>
+      <c r="C9" s="40" t="s">
+        <v>62</v>
+      </c>
+      <c r="D9" s="40" t="s">
+        <v>63</v>
+      </c>
+      <c r="E9" s="41" t="s">
+        <v>64</v>
+      </c>
+      <c r="F9" s="41" t="s">
+        <v>73</v>
+      </c>
+      <c r="G9" s="41" t="s">
+        <v>74</v>
+      </c>
+      <c r="H9" s="41" t="s">
+        <v>75</v>
+      </c>
+      <c r="I9" s="41" t="s">
+        <v>76</v>
+      </c>
+      <c r="J9" s="41" t="s">
+        <v>77</v>
+      </c>
+      <c r="K9" s="41" t="s">
+        <v>78</v>
+      </c>
+      <c r="L9" s="41" t="s">
+        <v>46</v>
+      </c>
+      <c r="M9" s="41" t="s">
+        <v>48</v>
+      </c>
+      <c r="N9" s="41" t="s">
+        <v>47</v>
+      </c>
+      <c r="O9" s="41" t="s">
+        <v>60</v>
+      </c>
+      <c r="P9" s="41" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q9" s="41" t="s">
+        <v>58</v>
+      </c>
+      <c r="R9" s="41" t="s">
+        <v>59</v>
+      </c>
+      <c r="S9" s="37"/>
+      <c r="T9" s="37"/>
+      <c r="U9" s="37"/>
+      <c r="V9" s="37"/>
+      <c r="W9" s="37"/>
+      <c r="X9" s="37"/>
+      <c r="Y9" s="37"/>
+      <c r="Z9" s="37"/>
+      <c r="AA9" s="37"/>
+      <c r="AB9" s="37"/>
+      <c r="AC9" s="37"/>
+      <c r="AD9" s="37"/>
+      <c r="AE9" s="37"/>
+      <c r="AF9" s="37"/>
+    </row>
+    <row r="10" spans="1:32" x14ac:dyDescent="0.45">
+      <c r="A10" s="5">
+        <v>1</v>
+      </c>
+      <c r="B10" s="13" t="s">
+        <v>79</v>
+      </c>
+      <c r="C10" s="8">
+        <v>7998579.2960000001</v>
+      </c>
+      <c r="D10" s="8">
+        <v>2289162.665</v>
+      </c>
+      <c r="E10" s="14">
+        <v>180</v>
+      </c>
+      <c r="F10" s="38">
+        <f>($C$6-C10)</f>
+        <v>-3096347.2960000001</v>
+      </c>
+      <c r="G10" s="38">
+        <f>($D$6-D10)</f>
+        <v>8276.3349999999627</v>
+      </c>
+      <c r="H10" s="38">
+        <f>ABS($E$6-E10)</f>
+        <v>180</v>
+      </c>
+      <c r="I10" s="38">
+        <f>(F10/2)+C10</f>
+        <v>6450405.648</v>
+      </c>
+      <c r="J10" s="38">
+        <f>(G10/2)+D10</f>
+        <v>2293300.8325</v>
+      </c>
+      <c r="K10" s="38">
+        <f>(H10/2)+E10</f>
+        <v>270</v>
+      </c>
+      <c r="L10" s="38">
+        <f>(F10^2+G10^2)^0.5</f>
+        <v>3096358.35703291</v>
+      </c>
+      <c r="M10" s="38">
+        <f>(L10^2+H10^2)^0.5</f>
+        <v>3096358.3622648623</v>
+      </c>
+      <c r="N10" s="38">
+        <f>ABS(H10/SIN(Q10))</f>
+        <v>3096358.3622648627</v>
+      </c>
+      <c r="O10" s="38">
+        <f>ATAN(G10/F10)</f>
+        <v>-2.6729286151006932E-3</v>
+      </c>
+      <c r="P10" s="38">
+        <f>ATAN(G10/F10)*180/PI()</f>
+        <v>-0.15314752858501782</v>
+      </c>
+      <c r="Q10" s="38">
+        <f>ABS(ATAN(H10/L10))</f>
+        <v>5.8132806039194982E-5</v>
+      </c>
+      <c r="R10" s="38">
+        <f>ABS(ATAN(H10/L10)*180/PI())</f>
+        <v>3.330764437298496E-3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:32" x14ac:dyDescent="0.45">
+      <c r="A11" s="5">
+        <v>2</v>
+      </c>
+      <c r="B11" s="13" t="s">
+        <v>80</v>
+      </c>
+      <c r="C11" s="8">
+        <v>3911674.574</v>
+      </c>
+      <c r="D11" s="8">
+        <v>2214042.8640000001</v>
+      </c>
+      <c r="E11" s="14">
+        <v>140</v>
+      </c>
+      <c r="F11" s="38">
+        <f t="shared" ref="F11:F12" si="1">($C$6-C11)</f>
+        <v>990557.42599999998</v>
+      </c>
+      <c r="G11" s="38">
+        <f t="shared" ref="G11:G12" si="2">($D$6-D11)</f>
+        <v>83396.13599999994</v>
+      </c>
+      <c r="H11" s="38">
+        <f>ABS($E$6-E11)</f>
+        <v>140</v>
+      </c>
+      <c r="I11" s="38">
+        <f>(F11/2)+C11</f>
+        <v>4406953.2870000005</v>
+      </c>
+      <c r="J11" s="38">
+        <f>(G11/2)+D11</f>
+        <v>2255740.932</v>
+      </c>
+      <c r="K11" s="38">
+        <f>(H11/2)+E11</f>
+        <v>210</v>
+      </c>
+      <c r="L11" s="38">
+        <f>(F11^2+G11^2)^0.5</f>
+        <v>994061.83394368179</v>
+      </c>
+      <c r="M11" s="38">
+        <f>(L11^2+H11^2)^0.5</f>
+        <v>994061.84380222333</v>
+      </c>
+      <c r="N11" s="38">
+        <f>ABS(H11/SIN(Q11))</f>
+        <v>994061.84380222333</v>
+      </c>
+      <c r="O11" s="38">
+        <f>ATAN(G11/F11)</f>
+        <v>8.3993038982769511E-2</v>
+      </c>
+      <c r="P11" s="38">
+        <f>ATAN(G11/F11)*180/PI()</f>
+        <v>4.8124466421904906</v>
+      </c>
+      <c r="Q11" s="38">
+        <f>ABS(ATAN(H11/L11))</f>
+        <v>1.4083630846077185E-4</v>
+      </c>
+      <c r="R11" s="38">
+        <f>ABS(ATAN(H11/L11)*180/PI())</f>
+        <v>8.0693260770048347E-3</v>
+      </c>
+    </row>
+    <row r="12" spans="1:32" x14ac:dyDescent="0.45">
+      <c r="A12" s="5">
+        <v>3</v>
+      </c>
+      <c r="B12" s="13" t="s">
+        <v>81</v>
+      </c>
+      <c r="C12" s="8">
+        <v>4892216.176</v>
+      </c>
+      <c r="D12" s="8">
+        <v>2306571.8050000002</v>
+      </c>
+      <c r="E12" s="14">
+        <v>90</v>
+      </c>
+      <c r="F12" s="38">
+        <f t="shared" si="1"/>
+        <v>10015.824000000022</v>
+      </c>
+      <c r="G12" s="38">
+        <f t="shared" si="2"/>
+        <v>-9132.8050000001676</v>
+      </c>
+      <c r="H12" s="38">
+        <f>ABS($E$6-E12)</f>
+        <v>90</v>
+      </c>
+      <c r="I12" s="38">
+        <f>(F12/2)+C12</f>
+        <v>4897224.0879999995</v>
+      </c>
+      <c r="J12" s="38">
+        <f>(G12/2)+D12</f>
+        <v>2302005.4024999999</v>
+      </c>
+      <c r="K12" s="38">
+        <f>(H12/2)+E12</f>
+        <v>135</v>
+      </c>
+      <c r="L12" s="38">
+        <f>(F12^2+G12^2)^0.5</f>
+        <v>13554.514287387967</v>
+      </c>
+      <c r="M12" s="38">
+        <f>(L12^2+H12^2)^0.5</f>
+        <v>13554.813077538345</v>
+      </c>
+      <c r="N12" s="38">
+        <f>ABS(H12/SIN(Q12))</f>
+        <v>13554.813077538343</v>
+      </c>
+      <c r="O12" s="38">
+        <f>ATAN(G12/F12)</f>
+        <v>-0.73931685465000996</v>
+      </c>
+      <c r="P12" s="38">
+        <f>ATAN(G12/F12)*180/PI()</f>
+        <v>-42.359735494332504</v>
+      </c>
+      <c r="Q12" s="38">
+        <f>ABS(ATAN(H12/L12))</f>
+        <v>6.63975672582914E-3</v>
+      </c>
+      <c r="R12" s="38">
+        <f>ABS(ATAN(H12/L12)*180/PI())</f>
+        <v>0.38043003738361181</v>
+      </c>
+    </row>
+    <row r="13" spans="1:32" x14ac:dyDescent="0.45">
+      <c r="A13" s="5">
+        <v>4</v>
+      </c>
+      <c r="B13" s="13"/>
+      <c r="C13" s="8"/>
+      <c r="D13" s="8"/>
+      <c r="E13" s="14"/>
+      <c r="F13" s="38"/>
+      <c r="G13" s="38"/>
+      <c r="H13" s="38"/>
+      <c r="I13" s="38"/>
+      <c r="J13" s="38"/>
+      <c r="K13" s="38"/>
+      <c r="L13" s="38"/>
+      <c r="M13" s="38"/>
+      <c r="N13" s="38"/>
+      <c r="O13" s="38"/>
+      <c r="P13" s="38"/>
+      <c r="Q13" s="38"/>
+      <c r="R13" s="38"/>
+    </row>
+    <row r="14" spans="1:32" x14ac:dyDescent="0.45">
+      <c r="A14" s="5">
+        <v>5</v>
+      </c>
+      <c r="B14" s="13"/>
+      <c r="C14" s="8"/>
+      <c r="D14" s="8"/>
+      <c r="E14" s="14"/>
+      <c r="F14" s="38"/>
+      <c r="G14" s="38"/>
+      <c r="H14" s="38"/>
+      <c r="I14" s="38"/>
+      <c r="J14" s="38"/>
+      <c r="K14" s="38"/>
+      <c r="L14" s="38"/>
+      <c r="M14" s="38"/>
+      <c r="N14" s="38"/>
+      <c r="O14" s="38"/>
+      <c r="P14" s="38"/>
+      <c r="Q14" s="38"/>
+      <c r="R14" s="38"/>
+    </row>
+    <row r="15" spans="1:32" x14ac:dyDescent="0.45">
+      <c r="A15" s="5">
+        <v>6</v>
+      </c>
+      <c r="B15" s="13"/>
+      <c r="C15" s="8"/>
+      <c r="D15" s="8"/>
+      <c r="E15" s="14"/>
+      <c r="F15" s="38"/>
+      <c r="G15" s="38"/>
+      <c r="H15" s="38"/>
+      <c r="I15" s="38"/>
+      <c r="J15" s="38"/>
+      <c r="K15" s="38"/>
+      <c r="L15" s="38"/>
+      <c r="M15" s="38"/>
+      <c r="N15" s="38"/>
+      <c r="O15" s="38"/>
+      <c r="P15" s="38"/>
+      <c r="Q15" s="38"/>
+      <c r="R15" s="38"/>
+    </row>
+    <row r="16" spans="1:32" x14ac:dyDescent="0.45">
+      <c r="A16" s="5">
+        <v>7</v>
+      </c>
+      <c r="B16" s="13"/>
+      <c r="C16" s="8"/>
+      <c r="D16" s="8"/>
+      <c r="E16" s="14"/>
+      <c r="F16" s="38"/>
+      <c r="G16" s="38"/>
+      <c r="H16" s="38"/>
+      <c r="I16" s="38"/>
+      <c r="J16" s="38"/>
+      <c r="K16" s="38"/>
+      <c r="L16" s="38"/>
+      <c r="M16" s="38"/>
+      <c r="N16" s="38"/>
+      <c r="O16" s="38"/>
+      <c r="P16" s="38"/>
+      <c r="Q16" s="38"/>
+      <c r="R16" s="38"/>
+    </row>
+    <row r="17" spans="1:18" x14ac:dyDescent="0.45">
+      <c r="A17" s="5">
+        <v>8</v>
+      </c>
+      <c r="B17" s="13"/>
+      <c r="C17" s="8"/>
+      <c r="D17" s="8"/>
+      <c r="E17" s="14"/>
+      <c r="F17" s="38"/>
+      <c r="G17" s="38"/>
+      <c r="H17" s="38"/>
+      <c r="I17" s="38"/>
+      <c r="J17" s="38"/>
+      <c r="K17" s="38"/>
+      <c r="L17" s="38"/>
+      <c r="M17" s="38"/>
+      <c r="N17" s="38"/>
+      <c r="O17" s="38"/>
+      <c r="P17" s="38"/>
+      <c r="Q17" s="38"/>
+      <c r="R17" s="38"/>
+    </row>
+    <row r="18" spans="1:18" x14ac:dyDescent="0.45">
+      <c r="A18" s="5">
+        <v>9</v>
+      </c>
+      <c r="B18" s="13"/>
+      <c r="C18" s="8"/>
+      <c r="D18" s="8"/>
+      <c r="E18" s="14"/>
+      <c r="F18" s="38"/>
+      <c r="G18" s="38"/>
+      <c r="H18" s="38"/>
+      <c r="I18" s="38"/>
+      <c r="J18" s="38"/>
+      <c r="K18" s="38"/>
+      <c r="L18" s="38"/>
+      <c r="M18" s="38"/>
+      <c r="N18" s="38"/>
+      <c r="O18" s="38"/>
+      <c r="P18" s="38"/>
+      <c r="Q18" s="38"/>
+      <c r="R18" s="38"/>
+    </row>
+    <row r="19" spans="1:18" x14ac:dyDescent="0.45">
+      <c r="A19" s="5">
+        <v>10</v>
+      </c>
+      <c r="B19" s="34"/>
+      <c r="C19" s="35"/>
+      <c r="D19" s="35"/>
+      <c r="E19" s="36"/>
+      <c r="F19" s="43"/>
+      <c r="G19" s="43"/>
+      <c r="H19" s="43"/>
+      <c r="I19" s="43"/>
+      <c r="J19" s="43"/>
+      <c r="K19" s="43"/>
+      <c r="L19" s="43"/>
+      <c r="M19" s="43"/>
+      <c r="N19" s="43"/>
+      <c r="O19" s="43"/>
+      <c r="P19" s="43"/>
+      <c r="Q19" s="43"/>
+      <c r="R19" s="43"/>
+    </row>
+    <row r="20" spans="1:18" x14ac:dyDescent="0.45">
+      <c r="B20" s="6" t="s">
+        <v>68</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A467452E-9DB9-4B6A-B4BF-ACF2268D9B4D}">
   <dimension ref="A2:X4"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
@@ -1473,7 +2134,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EF1F98EA-2567-4F71-99FA-C333BD6B7744}">
   <dimension ref="B2:E4"/>
   <sheetFormatPr defaultColWidth="13.53125" defaultRowHeight="16.5" x14ac:dyDescent="0.6"/>
